--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/177.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/177.xlsx
@@ -426,13 +426,13 @@
         <v>-6.156211214521705</v>
       </c>
       <c r="E2">
-        <v>-16.42857216374642</v>
+        <v>-18.04471208149985</v>
       </c>
       <c r="F2">
-        <v>4.508807720667904</v>
+        <v>4.437067426404413</v>
       </c>
       <c r="G2">
-        <v>-14.74541927349765</v>
+        <v>-17.09287745721176</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.921758815535885</v>
       </c>
       <c r="E3">
-        <v>-16.90826435843092</v>
+        <v>-17.44058194955856</v>
       </c>
       <c r="F3">
-        <v>4.719689249250075</v>
+        <v>4.819131727386433</v>
       </c>
       <c r="G3">
-        <v>-14.49766797697521</v>
+        <v>-16.0329235391756</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.722938085319824</v>
       </c>
       <c r="E4">
-        <v>-17.63887476940643</v>
+        <v>-19.75402082348708</v>
       </c>
       <c r="F4">
-        <v>4.407817961852162</v>
+        <v>4.630244706557885</v>
       </c>
       <c r="G4">
-        <v>-14.7658370631111</v>
+        <v>-16.05891959802273</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.572305682947521</v>
       </c>
       <c r="E5">
-        <v>-17.12511033628822</v>
+        <v>-18.95139861884159</v>
       </c>
       <c r="F5">
-        <v>4.779065551431731</v>
+        <v>4.964371813185469</v>
       </c>
       <c r="G5">
-        <v>-14.12245240082698</v>
+        <v>-16.7707216496942</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.446095435242355</v>
       </c>
       <c r="E6">
-        <v>-18.31492159706353</v>
+        <v>-22.01204928945775</v>
       </c>
       <c r="F6">
-        <v>4.929718744049739</v>
+        <v>4.94745308289083</v>
       </c>
       <c r="G6">
-        <v>-13.17740255264062</v>
+        <v>-14.29366885029978</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.330535575444444</v>
       </c>
       <c r="E7">
-        <v>-19.42365958767951</v>
+        <v>-21.32224042929134</v>
       </c>
       <c r="F7">
-        <v>5.16901987528447</v>
+        <v>5.275798079221144</v>
       </c>
       <c r="G7">
-        <v>-13.25575323391855</v>
+        <v>-15.26928165490469</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.198274119755263</v>
       </c>
       <c r="E8">
-        <v>-20.60203645158546</v>
+        <v>-21.963196111863</v>
       </c>
       <c r="F8">
-        <v>5.082910617250197</v>
+        <v>5.629306578841875</v>
       </c>
       <c r="G8">
-        <v>-11.49283807607356</v>
+        <v>-14.72460918423779</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.039064854999627</v>
       </c>
       <c r="E9">
-        <v>-20.74190289978636</v>
+        <v>-22.87609118706926</v>
       </c>
       <c r="F9">
-        <v>5.091251996306816</v>
+        <v>5.435799887857992</v>
       </c>
       <c r="G9">
-        <v>-11.38656956426295</v>
+        <v>-11.99590857622121</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.83759606387472</v>
       </c>
       <c r="E10">
-        <v>-21.30322083845913</v>
+        <v>-22.1948637851474</v>
       </c>
       <c r="F10">
-        <v>5.224817002097232</v>
+        <v>5.591916865884266</v>
       </c>
       <c r="G10">
-        <v>-11.08203910119648</v>
+        <v>-12.58349399344091</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.59850222549936</v>
       </c>
       <c r="E11">
-        <v>-21.44401562383161</v>
+        <v>-24.09239854926345</v>
       </c>
       <c r="F11">
-        <v>5.49417845531292</v>
+        <v>5.587845157975671</v>
       </c>
       <c r="G11">
-        <v>-10.14198321095611</v>
+        <v>-11.41645716939149</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.332806918709728</v>
       </c>
       <c r="E12">
-        <v>-23.12907891598178</v>
+        <v>-24.40017175672076</v>
       </c>
       <c r="F12">
-        <v>5.830104651860443</v>
+        <v>5.889566474161533</v>
       </c>
       <c r="G12">
-        <v>-10.34842883078506</v>
+        <v>-10.91165856447235</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.056478044620456</v>
       </c>
       <c r="E13">
-        <v>-24.25042417823512</v>
+        <v>-23.90436725151697</v>
       </c>
       <c r="F13">
-        <v>5.522509370434217</v>
+        <v>6.50653712246294</v>
       </c>
       <c r="G13">
-        <v>-8.77062944785949</v>
+        <v>-10.86366558578953</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.798261391876709</v>
       </c>
       <c r="E14">
-        <v>-24.04715003697881</v>
+        <v>-26.13920993056836</v>
       </c>
       <c r="F14">
-        <v>5.666780228213004</v>
+        <v>5.948572189158976</v>
       </c>
       <c r="G14">
-        <v>-8.581991252486278</v>
+        <v>-10.10411056998685</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.573275342487707</v>
       </c>
       <c r="E15">
-        <v>-25.71901735587063</v>
+        <v>-25.9953584252407</v>
       </c>
       <c r="F15">
-        <v>5.892781397169875</v>
+        <v>6.523256305812234</v>
       </c>
       <c r="G15">
-        <v>-7.483532379282863</v>
+        <v>-9.272160544331378</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.401262519325846</v>
       </c>
       <c r="E16">
-        <v>-25.77429643808226</v>
+        <v>-28.09822325781255</v>
       </c>
       <c r="F16">
-        <v>6.268252730425921</v>
+        <v>6.332167933761226</v>
       </c>
       <c r="G16">
-        <v>-7.495390753404532</v>
+        <v>-7.803562816564209</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.284926389311809</v>
       </c>
       <c r="E17">
-        <v>-28.28203401778388</v>
+        <v>-28.32235102187417</v>
       </c>
       <c r="F17">
-        <v>6.421064514206673</v>
+        <v>7.131210916337045</v>
       </c>
       <c r="G17">
-        <v>-8.003297960585057</v>
+        <v>-8.836601999366087</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.225377857062559</v>
       </c>
       <c r="E18">
-        <v>-28.08740926188223</v>
+        <v>-29.71117512986457</v>
       </c>
       <c r="F18">
-        <v>6.420641664727251</v>
+        <v>6.682990468149373</v>
       </c>
       <c r="G18">
-        <v>-6.651572421990778</v>
+        <v>-8.385609691096711</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.22234071694136</v>
       </c>
       <c r="E19">
-        <v>-29.32091576835755</v>
+        <v>-30.59249089157835</v>
       </c>
       <c r="F19">
-        <v>7.009262393436376</v>
+        <v>7.540864958071936</v>
       </c>
       <c r="G19">
-        <v>-6.578127969202047</v>
+        <v>-7.568997422924688</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.267877032807011</v>
       </c>
       <c r="E20">
-        <v>-30.38097719186509</v>
+        <v>-29.92552139006963</v>
       </c>
       <c r="F20">
-        <v>6.86153272193827</v>
+        <v>7.027630214643644</v>
       </c>
       <c r="G20">
-        <v>-7.064937069660796</v>
+        <v>-8.490894970882152</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.363427310862494</v>
       </c>
       <c r="E21">
-        <v>-30.26948163332224</v>
+        <v>-32.05432758599441</v>
       </c>
       <c r="F21">
-        <v>6.880698730926918</v>
+        <v>6.805021343757644</v>
       </c>
       <c r="G21">
-        <v>-6.682181726046879</v>
+        <v>-8.325212098278248</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.496793997519119</v>
       </c>
       <c r="E22">
-        <v>-31.04864634260799</v>
+        <v>-32.86707545852106</v>
       </c>
       <c r="F22">
-        <v>7.1805655274858</v>
+        <v>7.127519297848155</v>
       </c>
       <c r="G22">
-        <v>-6.141718614033161</v>
+        <v>-7.077778675807629</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.663820189343229</v>
       </c>
       <c r="E23">
-        <v>-30.30369425445019</v>
+        <v>-32.21122562493817</v>
       </c>
       <c r="F23">
-        <v>6.927733212909554</v>
+        <v>6.757633695355865</v>
       </c>
       <c r="G23">
-        <v>-5.609962236787728</v>
+        <v>-7.41713607794724</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.854073288753805</v>
       </c>
       <c r="E24">
-        <v>-29.99348925645076</v>
+        <v>-33.83547377540233</v>
       </c>
       <c r="F24">
-        <v>6.736792125508681</v>
+        <v>6.880294885918481</v>
       </c>
       <c r="G24">
-        <v>-5.2270711608067</v>
+        <v>-6.394121227038275</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.056941426299812</v>
       </c>
       <c r="E25">
-        <v>-31.95371168625499</v>
+        <v>-32.33342876027216</v>
       </c>
       <c r="F25">
-        <v>7.023683619502368</v>
+        <v>6.982374234404046</v>
       </c>
       <c r="G25">
-        <v>-6.003281531217459</v>
+        <v>-7.245961010293684</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.269350864336142</v>
       </c>
       <c r="E26">
-        <v>-31.58142130961041</v>
+        <v>-34.06911586335408</v>
       </c>
       <c r="F26">
-        <v>7.127734681852655</v>
+        <v>6.793265494747336</v>
       </c>
       <c r="G26">
-        <v>-4.893874683915673</v>
+        <v>-7.098794018890922</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.479904842870343</v>
       </c>
       <c r="E27">
-        <v>-32.04316263332851</v>
+        <v>-32.84337342556491</v>
       </c>
       <c r="F27">
-        <v>6.778149021784468</v>
+        <v>6.751205433045095</v>
       </c>
       <c r="G27">
-        <v>-5.788688658816361</v>
+        <v>-6.951918355495617</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.690590929635547</v>
       </c>
       <c r="E28">
-        <v>-31.37106689924311</v>
+        <v>-34.07029553083308</v>
       </c>
       <c r="F28">
-        <v>6.82101043867992</v>
+        <v>6.491103908316982</v>
       </c>
       <c r="G28">
-        <v>-4.85309538396293</v>
+        <v>-6.489302721837861</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.894559328625334</v>
       </c>
       <c r="E29">
-        <v>-32.48307671232963</v>
+        <v>-33.03349461406594</v>
       </c>
       <c r="F29">
-        <v>6.810138297570428</v>
+        <v>6.528918054459931</v>
       </c>
       <c r="G29">
-        <v>-4.590982940891134</v>
+        <v>-6.929916469841621</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.094178391672308</v>
       </c>
       <c r="E30">
-        <v>-30.79043049045362</v>
+        <v>-31.51840985803068</v>
       </c>
       <c r="F30">
-        <v>6.471853962914817</v>
+        <v>6.554916170767784</v>
       </c>
       <c r="G30">
-        <v>-5.472726882002779</v>
+        <v>-6.2036820948917</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.290340482911756</v>
       </c>
       <c r="E31">
-        <v>-31.7874012140863</v>
+        <v>-33.49549858927648</v>
       </c>
       <c r="F31">
-        <v>6.321302127475396</v>
+        <v>6.514021716619307</v>
       </c>
       <c r="G31">
-        <v>-5.625028529536951</v>
+        <v>-5.813110553259564</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.478594981235288</v>
       </c>
       <c r="E32">
-        <v>-30.90380310147265</v>
+        <v>-33.04454861911866</v>
       </c>
       <c r="F32">
-        <v>6.808090565821765</v>
+        <v>6.070979986775122</v>
       </c>
       <c r="G32">
-        <v>-5.023588479235396</v>
+        <v>-5.935872202946818</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.663500180448017</v>
       </c>
       <c r="E33">
-        <v>-31.62676944832322</v>
+        <v>-33.01265910515664</v>
       </c>
       <c r="F33">
-        <v>6.465788369258683</v>
+        <v>6.523343409637584</v>
       </c>
       <c r="G33">
-        <v>-5.382031176408906</v>
+        <v>-6.227835835146223</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.836292259148966</v>
       </c>
       <c r="E34">
-        <v>-30.3223606243098</v>
+        <v>-31.49738415321306</v>
       </c>
       <c r="F34">
-        <v>6.429326707967521</v>
+        <v>5.924967052489351</v>
       </c>
       <c r="G34">
-        <v>-5.163230600627394</v>
+        <v>-6.198431569666417</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.999178785782781</v>
       </c>
       <c r="E35">
-        <v>-29.43980632495493</v>
+        <v>-31.61467842272274</v>
       </c>
       <c r="F35">
-        <v>6.292892027058328</v>
+        <v>6.707149901889402</v>
       </c>
       <c r="G35">
-        <v>-5.416858115482039</v>
+        <v>-6.932253714992346</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.147323014643447</v>
       </c>
       <c r="E36">
-        <v>-28.36808860935164</v>
+        <v>-31.17534398839459</v>
       </c>
       <c r="F36">
-        <v>6.365949964643465</v>
+        <v>6.910966518382796</v>
       </c>
       <c r="G36">
-        <v>-5.855442499070225</v>
+        <v>-4.918137672172992</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.275436272584041</v>
       </c>
       <c r="E37">
-        <v>-28.5451791138956</v>
+        <v>-30.13109373188483</v>
       </c>
       <c r="F37">
-        <v>6.243816148150691</v>
+        <v>6.287485255063017</v>
       </c>
       <c r="G37">
-        <v>-5.158840817242321</v>
+        <v>-7.895258306910942</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.387119528907185</v>
       </c>
       <c r="E38">
-        <v>-28.21551979155922</v>
+        <v>-29.76296275861629</v>
       </c>
       <c r="F38">
-        <v>7.053842131250081</v>
+        <v>6.0321633547877</v>
       </c>
       <c r="G38">
-        <v>-4.792227693677891</v>
+        <v>-6.931661127340816</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.475199926435054</v>
       </c>
       <c r="E39">
-        <v>-28.08965085651602</v>
+        <v>-29.72935468876836</v>
       </c>
       <c r="F39">
-        <v>6.491078569022336</v>
+        <v>6.514324204449156</v>
       </c>
       <c r="G39">
-        <v>-5.129459725581289</v>
+        <v>-5.947525323245053</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.54748706747485</v>
       </c>
       <c r="E40">
-        <v>-26.98233027826444</v>
+        <v>-28.68807963968165</v>
       </c>
       <c r="F40">
-        <v>6.634264588249047</v>
+        <v>6.830751813765788</v>
       </c>
       <c r="G40">
-        <v>-5.504355834084977</v>
+        <v>-6.387890780333367</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.601451860166698</v>
       </c>
       <c r="E41">
-        <v>-28.01493103538946</v>
+        <v>-29.06236254488961</v>
       </c>
       <c r="F41">
-        <v>6.331360243744352</v>
+        <v>6.577878322835741</v>
       </c>
       <c r="G41">
-        <v>-5.130833601980087</v>
+        <v>-6.047917616723452</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.643073152227476</v>
       </c>
       <c r="E42">
-        <v>-26.0791351943826</v>
+        <v>-27.54398332401377</v>
       </c>
       <c r="F42">
-        <v>6.306491309754207</v>
+        <v>6.711980204931492</v>
       </c>
       <c r="G42">
-        <v>-5.713006277243082</v>
+        <v>-7.631646186709856</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.680417734241527</v>
       </c>
       <c r="E43">
-        <v>-25.56728177729562</v>
+        <v>-28.0519694242982</v>
       </c>
       <c r="F43">
-        <v>6.802308455524495</v>
+        <v>6.224642220632465</v>
       </c>
       <c r="G43">
-        <v>-6.522782268876511</v>
+        <v>-7.008399572941123</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.712895840124091</v>
       </c>
       <c r="E44">
-        <v>-26.0058101432504</v>
+        <v>-26.83782667267968</v>
       </c>
       <c r="F44">
-        <v>6.635248069622535</v>
+        <v>6.500121529799495</v>
       </c>
       <c r="G44">
-        <v>-5.973625664276667</v>
+        <v>-7.972880668170233</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.753387127854007</v>
       </c>
       <c r="E45">
-        <v>-23.9966620802673</v>
+        <v>-26.58201770446038</v>
       </c>
       <c r="F45">
-        <v>6.311479983387841</v>
+        <v>6.419365197759407</v>
       </c>
       <c r="G45">
-        <v>-6.188297989770708</v>
+        <v>-7.162674305616699</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.797995967678592</v>
       </c>
       <c r="E46">
-        <v>-24.52997140720262</v>
+        <v>-27.81791977368576</v>
       </c>
       <c r="F46">
-        <v>6.734419734047354</v>
+        <v>6.934790206468752</v>
       </c>
       <c r="G46">
-        <v>-6.584331931542641</v>
+        <v>-7.701432486677692</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.855952394554678</v>
       </c>
       <c r="E47">
-        <v>-24.87489621541885</v>
+        <v>-26.05797363534476</v>
       </c>
       <c r="F47">
-        <v>6.393428845982255</v>
+        <v>7.042874967785663</v>
       </c>
       <c r="G47">
-        <v>-6.62730612318792</v>
+        <v>-8.24671575299659</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.928692479678648</v>
       </c>
       <c r="E48">
-        <v>-23.36974013864541</v>
+        <v>-26.1470306051796</v>
       </c>
       <c r="F48">
-        <v>6.771582977059055</v>
+        <v>6.894641677806447</v>
       </c>
       <c r="G48">
-        <v>-7.225289963946475</v>
+        <v>-9.230729066907399</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.014056986347086</v>
       </c>
       <c r="E49">
-        <v>-22.56036145078048</v>
+        <v>-24.81349010787484</v>
       </c>
       <c r="F49">
-        <v>6.574837607478097</v>
+        <v>7.360042167764806</v>
       </c>
       <c r="G49">
-        <v>-6.595352737642875</v>
+        <v>-8.725059788511421</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.120938260850103</v>
       </c>
       <c r="E50">
-        <v>-23.5869982076374</v>
+        <v>-23.85389740870148</v>
       </c>
       <c r="F50">
-        <v>6.71525530876462</v>
+        <v>6.694572109508981</v>
       </c>
       <c r="G50">
-        <v>-7.067671580276234</v>
+        <v>-8.317230372983065</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.241066393062413</v>
       </c>
       <c r="E51">
-        <v>-21.24186907260321</v>
+        <v>-24.28724520039149</v>
       </c>
       <c r="F51">
-        <v>6.867793111422001</v>
+        <v>6.790731565282633</v>
       </c>
       <c r="G51">
-        <v>-7.509417534854424</v>
+        <v>-9.270756873022727</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.383045186942432</v>
       </c>
       <c r="E52">
-        <v>-21.01997837470137</v>
+        <v>-22.93480738105272</v>
       </c>
       <c r="F52">
-        <v>6.45121827483664</v>
+        <v>6.918392515420292</v>
       </c>
       <c r="G52">
-        <v>-7.572476806286462</v>
+        <v>-8.346621396280714</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.539980781279491</v>
       </c>
       <c r="E53">
-        <v>-20.3050410122664</v>
+        <v>-23.0038711381437</v>
       </c>
       <c r="F53">
-        <v>6.834136193307082</v>
+        <v>7.034684040791011</v>
       </c>
       <c r="G53">
-        <v>-7.343483060789534</v>
+        <v>-8.348402469780842</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.712444262348894</v>
       </c>
       <c r="E54">
-        <v>-20.97364755712889</v>
+        <v>-22.31637632819521</v>
       </c>
       <c r="F54">
-        <v>6.986993904559382</v>
+        <v>6.4242778535091</v>
       </c>
       <c r="G54">
-        <v>-6.967957948633386</v>
+        <v>-10.01407035240975</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.903238381801557</v>
       </c>
       <c r="E55">
-        <v>-20.36430062313078</v>
+        <v>-21.49014718854774</v>
       </c>
       <c r="F55">
-        <v>6.645583334426693</v>
+        <v>6.402432214111528</v>
       </c>
       <c r="G55">
-        <v>-7.216937457550894</v>
+        <v>-8.653777121959834</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.103051516706179</v>
       </c>
       <c r="E56">
-        <v>-19.59233165904321</v>
+        <v>-21.21322194603069</v>
       </c>
       <c r="F56">
-        <v>6.681691829298712</v>
+        <v>6.651408204783679</v>
       </c>
       <c r="G56">
-        <v>-8.532299963941817</v>
+        <v>-9.939801573781738</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.320105301203538</v>
       </c>
       <c r="E57">
-        <v>-18.08620648883213</v>
+        <v>-19.66008668714598</v>
       </c>
       <c r="F57">
-        <v>6.772910122616193</v>
+        <v>7.156342745509154</v>
       </c>
       <c r="G57">
-        <v>-8.686962030445489</v>
+        <v>-8.305875201783365</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.541569328070914</v>
       </c>
       <c r="E58">
-        <v>-17.99500755079166</v>
+        <v>-21.13376986956611</v>
       </c>
       <c r="F58">
-        <v>6.822573556418459</v>
+        <v>6.727473599902235</v>
       </c>
       <c r="G58">
-        <v>-7.714366788099625</v>
+        <v>-10.12598996545589</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.771750670309814</v>
       </c>
       <c r="E59">
-        <v>-19.25535432271044</v>
+        <v>-19.0737308156848</v>
       </c>
       <c r="F59">
-        <v>6.893344622661702</v>
+        <v>7.392821712802572</v>
       </c>
       <c r="G59">
-        <v>-8.233228590469597</v>
+        <v>-10.58363978080474</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.006150239495895</v>
       </c>
       <c r="E60">
-        <v>-18.11580459494626</v>
+        <v>-19.94198419412346</v>
       </c>
       <c r="F60">
-        <v>6.75386764268895</v>
+        <v>6.420914062144706</v>
       </c>
       <c r="G60">
-        <v>-9.137358440517795</v>
+        <v>-9.970364530200289</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.236758933413954</v>
       </c>
       <c r="E61">
-        <v>-18.41542654918976</v>
+        <v>-19.69390080256125</v>
       </c>
       <c r="F61">
-        <v>6.490991465196987</v>
+        <v>6.671513351380183</v>
       </c>
       <c r="G61">
-        <v>-9.101071550861842</v>
+        <v>-10.30852020430915</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.469594056037467</v>
       </c>
       <c r="E62">
-        <v>-17.72207189387536</v>
+        <v>-18.42694245859127</v>
       </c>
       <c r="F62">
-        <v>6.792810971149605</v>
+        <v>7.331326412106058</v>
       </c>
       <c r="G62">
-        <v>-8.997269395477995</v>
+        <v>-9.20297345310615</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.691056628967836</v>
       </c>
       <c r="E63">
-        <v>-17.40296844445086</v>
+        <v>-17.5233171696787</v>
       </c>
       <c r="F63">
-        <v>6.248906178962913</v>
+        <v>7.64103118981165</v>
       </c>
       <c r="G63">
-        <v>-9.212090695521303</v>
+        <v>-9.765067669673465</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.907892747623798</v>
       </c>
       <c r="E64">
-        <v>-16.89303962881714</v>
+        <v>-18.49387783289864</v>
       </c>
       <c r="F64">
-        <v>6.786721621904741</v>
+        <v>6.98127514249873</v>
       </c>
       <c r="G64">
-        <v>-9.693960462035459</v>
+        <v>-10.90764287273321</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.11055841803393</v>
       </c>
       <c r="E65">
-        <v>-17.47062384612545</v>
+        <v>-18.46110979497914</v>
       </c>
       <c r="F65">
-        <v>6.537940427060189</v>
+        <v>6.753493888092906</v>
       </c>
       <c r="G65">
-        <v>-9.740341205040648</v>
+        <v>-11.09599636119004</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.29670892590452</v>
       </c>
       <c r="E66">
-        <v>-16.339768788456</v>
+        <v>-18.18222825169077</v>
       </c>
       <c r="F66">
-        <v>6.242254614118067</v>
+        <v>6.40396999255542</v>
       </c>
       <c r="G66">
-        <v>-9.323891128928031</v>
+        <v>-10.7311444478525</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.46917422270983</v>
       </c>
       <c r="E67">
-        <v>-16.58898429852012</v>
+        <v>-17.46133594593572</v>
       </c>
       <c r="F67">
-        <v>6.553680880153742</v>
+        <v>6.656358869475342</v>
       </c>
       <c r="G67">
-        <v>-9.202122642902557</v>
+        <v>-11.21875138978622</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.61554683132737</v>
       </c>
       <c r="E68">
-        <v>-16.32479312491263</v>
+        <v>-17.43051062336551</v>
       </c>
       <c r="F68">
-        <v>6.523215129458433</v>
+        <v>7.159202918392437</v>
       </c>
       <c r="G68">
-        <v>-8.941443666049265</v>
+        <v>-10.22970273611018</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.74384472635487</v>
       </c>
       <c r="E69">
-        <v>-16.32292739362147</v>
+        <v>-17.34795201373167</v>
       </c>
       <c r="F69">
-        <v>6.292641801523688</v>
+        <v>6.46820985560339</v>
       </c>
       <c r="G69">
-        <v>-10.48567742775216</v>
+        <v>-12.12933018254492</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.84015020329084</v>
       </c>
       <c r="E70">
-        <v>-15.5010637029174</v>
+        <v>-17.36817617864992</v>
       </c>
       <c r="F70">
-        <v>6.21999404377065</v>
+        <v>6.780404219008053</v>
       </c>
       <c r="G70">
-        <v>-10.05941820520668</v>
+        <v>-10.56207488716193</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.90766090782662</v>
       </c>
       <c r="E71">
-        <v>-17.15854405988685</v>
+        <v>-17.58285301745754</v>
       </c>
       <c r="F71">
-        <v>6.026774003557461</v>
+        <v>6.977768817601948</v>
       </c>
       <c r="G71">
-        <v>-9.607134784176994</v>
+        <v>-11.91934227898894</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.94405104444543</v>
       </c>
       <c r="E72">
-        <v>-16.71288334736998</v>
+        <v>-16.75620272972736</v>
       </c>
       <c r="F72">
-        <v>6.336062266607292</v>
+        <v>6.546201037115121</v>
       </c>
       <c r="G72">
-        <v>-10.59803734335503</v>
+        <v>-11.33859975939891</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.93972348876801</v>
       </c>
       <c r="E73">
-        <v>-16.17749997933915</v>
+        <v>-17.95558718455488</v>
       </c>
       <c r="F73">
-        <v>6.150033834956113</v>
+        <v>6.576644615927614</v>
       </c>
       <c r="G73">
-        <v>-10.04569268340087</v>
+        <v>-12.33242221974258</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.90348818295911</v>
       </c>
       <c r="E74">
-        <v>-15.81959656461693</v>
+        <v>-17.90585548300265</v>
       </c>
       <c r="F74">
-        <v>5.707825134423448</v>
+        <v>6.449191131264878</v>
       </c>
       <c r="G74">
-        <v>-9.698174786506952</v>
+        <v>-12.52392072646173</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.82311823553179</v>
       </c>
       <c r="E75">
-        <v>-16.10600443170605</v>
+        <v>-17.13473334355452</v>
       </c>
       <c r="F75">
-        <v>5.977620523059966</v>
+        <v>5.904155573054561</v>
       </c>
       <c r="G75">
-        <v>-9.448937055037382</v>
+        <v>-11.04658315847088</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.70708228454383</v>
       </c>
       <c r="E76">
-        <v>-15.13981374590351</v>
+        <v>-19.07978085695905</v>
       </c>
       <c r="F76">
-        <v>5.363019098808056</v>
+        <v>6.389746729728858</v>
       </c>
       <c r="G76">
-        <v>-9.924745212669132</v>
+        <v>-10.40255625035214</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.55332882468017</v>
       </c>
       <c r="E77">
-        <v>-16.65518606003826</v>
+        <v>-17.75919179531623</v>
       </c>
       <c r="F77">
-        <v>5.71491221839504</v>
+        <v>5.705554100140708</v>
       </c>
       <c r="G77">
-        <v>-9.711195162112904</v>
+        <v>-11.92365260928108</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.36168531214732</v>
       </c>
       <c r="E78">
-        <v>-16.66763030661133</v>
+        <v>-16.0991256796884</v>
       </c>
       <c r="F78">
-        <v>5.744012814591239</v>
+        <v>5.95096675250312</v>
       </c>
       <c r="G78">
-        <v>-9.055875983159712</v>
+        <v>-11.3650013600746</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.1442600442645</v>
       </c>
       <c r="E79">
-        <v>-16.84045951711407</v>
+        <v>-18.41701151509245</v>
       </c>
       <c r="F79">
-        <v>5.520382453389781</v>
+        <v>6.093962727019979</v>
       </c>
       <c r="G79">
-        <v>-9.421002671777011</v>
+        <v>-11.00501594867979</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.894713895508476</v>
       </c>
       <c r="E80">
-        <v>-17.69838344634123</v>
+        <v>-20.56944049567824</v>
       </c>
       <c r="F80">
-        <v>5.016610352806239</v>
+        <v>5.857401407018958</v>
       </c>
       <c r="G80">
-        <v>-8.860596833434723</v>
+        <v>-10.54469452308075</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.627745833214105</v>
       </c>
       <c r="E81">
-        <v>-17.72579429950966</v>
+        <v>-18.15313280619149</v>
       </c>
       <c r="F81">
-        <v>5.357205314392478</v>
+        <v>6.223329328428566</v>
       </c>
       <c r="G81">
-        <v>-8.990297386572291</v>
+        <v>-11.02371059934006</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.339697810180661</v>
       </c>
       <c r="E82">
-        <v>-17.18350500861713</v>
+        <v>-19.00276057103659</v>
       </c>
       <c r="F82">
-        <v>5.160426686987296</v>
+        <v>5.910745373368704</v>
       </c>
       <c r="G82">
-        <v>-7.91666429436787</v>
+        <v>-10.31438980155027</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.038991741113248</v>
       </c>
       <c r="E83">
-        <v>-18.80504739586171</v>
+        <v>-19.89441710314689</v>
       </c>
       <c r="F83">
-        <v>5.063947322618724</v>
+        <v>5.55852284295131</v>
       </c>
       <c r="G83">
-        <v>-8.322894716400759</v>
+        <v>-10.65671014194753</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.734753061415233</v>
       </c>
       <c r="E84">
-        <v>-19.707332256468</v>
+        <v>-20.16850752093514</v>
       </c>
       <c r="F84">
-        <v>5.275802830338891</v>
+        <v>5.613749835634514</v>
       </c>
       <c r="G84">
-        <v>-7.59823947167307</v>
+        <v>-10.12442407741581</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.425566552842902</v>
       </c>
       <c r="E85">
-        <v>-21.16815004423234</v>
+        <v>-20.86678009902188</v>
       </c>
       <c r="F85">
-        <v>5.220232173472036</v>
+        <v>5.173568278673613</v>
       </c>
       <c r="G85">
-        <v>-7.764389131198013</v>
+        <v>-9.967795546861815</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.13073693640248</v>
       </c>
       <c r="E86">
-        <v>-21.85563579723281</v>
+        <v>-22.50475178996629</v>
       </c>
       <c r="F86">
-        <v>5.147191656651969</v>
+        <v>5.495828676876808</v>
       </c>
       <c r="G86">
-        <v>-7.953623224768293</v>
+        <v>-10.19480958612626</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.848986365936717</v>
       </c>
       <c r="E87">
-        <v>-22.21055947605798</v>
+        <v>-22.00761138493023</v>
       </c>
       <c r="F87">
-        <v>5.108099459835261</v>
+        <v>5.399604289160623</v>
       </c>
       <c r="G87">
-        <v>-7.656528246983018</v>
+        <v>-8.227819159058429</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.597210996473711</v>
       </c>
       <c r="E88">
-        <v>-23.45924542740702</v>
+        <v>-24.93915073311369</v>
       </c>
       <c r="F88">
-        <v>4.889747590449963</v>
+        <v>5.464080124389993</v>
       </c>
       <c r="G88">
-        <v>-6.492752310289782</v>
+        <v>-9.864996486776366</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.382144967486678</v>
       </c>
       <c r="E89">
-        <v>-25.287662092744</v>
+        <v>-26.21042018433897</v>
       </c>
       <c r="F89">
-        <v>5.163769890174788</v>
+        <v>5.392537793365932</v>
       </c>
       <c r="G89">
-        <v>-6.990234609567142</v>
+        <v>-8.271303174716756</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.208730205228899</v>
       </c>
       <c r="E90">
-        <v>-26.01719019843168</v>
+        <v>-26.26248857847916</v>
       </c>
       <c r="F90">
-        <v>5.042808016059439</v>
+        <v>5.000683022414665</v>
       </c>
       <c r="G90">
-        <v>-6.567905004576777</v>
+        <v>-7.991333649006131</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.093462396858019</v>
       </c>
       <c r="E91">
-        <v>-28.06527860940674</v>
+        <v>-29.38287434973049</v>
       </c>
       <c r="F91">
-        <v>4.657539878010485</v>
+        <v>5.458934663870731</v>
       </c>
       <c r="G91">
-        <v>-5.622207944737491</v>
+        <v>-9.077421013529291</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.031659570672054</v>
       </c>
       <c r="E92">
-        <v>-29.01592304394095</v>
+        <v>-30.03645088936153</v>
       </c>
       <c r="F92">
-        <v>4.255590565554207</v>
+        <v>5.015707640434439</v>
       </c>
       <c r="G92">
-        <v>-6.596253206029556</v>
+        <v>-7.791519051892339</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.037765098595719</v>
       </c>
       <c r="E93">
-        <v>-30.80100221302453</v>
+        <v>-30.92918746252265</v>
       </c>
       <c r="F93">
-        <v>4.500740322734655</v>
+        <v>5.006262418354758</v>
       </c>
       <c r="G93">
-        <v>-7.270939076387485</v>
+        <v>-6.939497188632272</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.103038327618829</v>
       </c>
       <c r="E94">
-        <v>-32.64628517980308</v>
+        <v>-33.91541492705974</v>
       </c>
       <c r="F94">
-        <v>4.239259390154195</v>
+        <v>4.839694564992499</v>
       </c>
       <c r="G94">
-        <v>-5.443385516888219</v>
+        <v>-7.201788401163189</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.229304724890602</v>
       </c>
       <c r="E95">
-        <v>-34.20949402911785</v>
+        <v>-35.16715759836395</v>
       </c>
       <c r="F95">
-        <v>4.035521958956572</v>
+        <v>4.969911616477677</v>
       </c>
       <c r="G95">
-        <v>-5.718074722463706</v>
+        <v>-7.264129284213204</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.416931200301799</v>
       </c>
       <c r="E96">
-        <v>-36.66292841275649</v>
+        <v>-37.89130642241813</v>
       </c>
       <c r="F96">
-        <v>4.067249923266486</v>
+        <v>4.185414972735169</v>
       </c>
       <c r="G96">
-        <v>-5.579799856379427</v>
+        <v>-6.517859487659615</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.648331284436422</v>
       </c>
       <c r="E97">
-        <v>-38.98712920516424</v>
+        <v>-39.03162825500061</v>
       </c>
       <c r="F97">
-        <v>3.254509468228031</v>
+        <v>3.991512355272425</v>
       </c>
       <c r="G97">
-        <v>-5.483840383378113</v>
+        <v>-7.054710794489988</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.937173175585732</v>
       </c>
       <c r="E98">
-        <v>-41.01869774295933</v>
+        <v>-38.89505174316628</v>
       </c>
       <c r="F98">
-        <v>3.488159936756475</v>
+        <v>4.033745040919449</v>
       </c>
       <c r="G98">
-        <v>-5.19718355567816</v>
+        <v>-6.712582465734006</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.253656465536437</v>
       </c>
       <c r="E99">
-        <v>-42.67720606352852</v>
+        <v>-43.82233487127014</v>
       </c>
       <c r="F99">
-        <v>2.863654015709406</v>
+        <v>4.013438763671684</v>
       </c>
       <c r="G99">
-        <v>-4.484085425428067</v>
+        <v>-6.093017178604943</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.623954714687477</v>
       </c>
       <c r="E100">
-        <v>-44.23991904493945</v>
+        <v>-45.61367239143232</v>
       </c>
       <c r="F100">
-        <v>2.428012943608069</v>
+        <v>3.564546824175865</v>
       </c>
       <c r="G100">
-        <v>-5.559191710397465</v>
+        <v>-6.641528226824629</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.004170651626795</v>
       </c>
       <c r="E101">
-        <v>-47.56409520348396</v>
+        <v>-47.87876527685495</v>
       </c>
       <c r="F101">
-        <v>2.713605798751096</v>
+        <v>3.092347484722524</v>
       </c>
       <c r="G101">
-        <v>-5.085644655369035</v>
+        <v>-6.531154638545328</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.449827859888332</v>
       </c>
       <c r="E102">
-        <v>-48.75529104518711</v>
+        <v>-50.39249176343171</v>
       </c>
       <c r="F102">
-        <v>2.667222219899705</v>
+        <v>2.914004777878973</v>
       </c>
       <c r="G102">
-        <v>-4.490928323057741</v>
+        <v>-6.825021834429813</v>
       </c>
     </row>
   </sheetData>
